--- a/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D01_sqp_top_terms.xlsx
+++ b/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D01_sqp_top_terms.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19T11:20:30</t>
+          <t>2026-08-19T11:34:56</t>
         </is>
       </c>
     </row>

--- a/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D01_sqp_top_terms.xlsx
+++ b/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D01_sqp_top_terms.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19T11:34:56</t>
+          <t>2026-08-19T11:46:28</t>
         </is>
       </c>
     </row>

--- a/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D01_sqp_top_terms.xlsx
+++ b/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D01_sqp_top_terms.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19T11:46:28</t>
+          <t>2026-08-19T11:52:27</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>1_account_separation=PASS; 3_one_place_is_enough=PASS; 4_dual_method_independent=PASS; 5_directional_add_logic=PASS; 6_zero_manual_lookup=PASS; 7_monthly_cadence=PASS</t>
+          <t>1_account_separation=PASS; 2_sku_mismatch_never_paired=PASS; 3_one_place_is_enough=PASS; 4_dual_method_independent=PASS; 5_directional_add_logic=PASS; 6_zero_manual_lookup=PASS; 7_monthly_cadence=PASS</t>
         </is>
       </c>
     </row>

--- a/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D01_sqp_top_terms.xlsx
+++ b/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D01_sqp_top_terms.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19T11:52:27</t>
+          <t>2026-08-19T12:03:23</t>
         </is>
       </c>
     </row>

--- a/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D01_sqp_top_terms.xlsx
+++ b/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D01_sqp_top_terms.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19T12:03:23</t>
+          <t>2026-08-19T12:11:57</t>
         </is>
       </c>
     </row>

--- a/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D01_sqp_top_terms.xlsx
+++ b/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D01_sqp_top_terms.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19T12:11:57</t>
+          <t>2026-08-19T12:26:43</t>
         </is>
       </c>
     </row>

--- a/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D01_sqp_top_terms.xlsx
+++ b/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D01_sqp_top_terms.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19T13:42:26</t>
+          <t>2026-08-19T14:02:40</t>
         </is>
       </c>
     </row>

--- a/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D01_sqp_top_terms.xlsx
+++ b/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D01_sqp_top_terms.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19T14:02:40</t>
+          <t>2026-08-19T14:35:18</t>
         </is>
       </c>
     </row>

--- a/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D01_sqp_top_terms.xlsx
+++ b/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D01_sqp_top_terms.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -496,7 +496,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19T14:35:18</t>
+          <t>2026-08-19T15:18:23</t>
         </is>
       </c>
     </row>
@@ -611,70 +611,82 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Months kept separate</t>
+          <t>Minimum searches (Part B)</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Source Step 4: the last 3 months are checked one month at a time, never combined. Each weekly row is assigned to the month containing its start_date. Phase 2 audits the de-duplicated union of the confirmed terms across those months.</t>
+          <t>a keyword reaches the Part B to-do list only if at least 10 people searched it in a month. Confirmed by Abiraj 2026-08-19; the source sets no floor. Phase 1 (D01) is unfiltered.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Rate denominators</t>
+          <t>Months kept separate</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Verified against Amazon's own stored columns: asin_share = ASIN impressions / total query impressions · click_rate = total clicks / SEARCH VOLUME (not impressions) · asin_click_share = ASIN clicks / total clicks. Recomputed from summed numerator and denominator, never averaged across weeks.</t>
+          <t>Source Step 4: the last 3 months are checked one month at a time, never combined. Each weekly row is assigned to the month containing its start_date. Phase 2 audits the de-duplicated union of the confirmed terms across those months.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>SCOPE BOUNDARY</t>
+          <t>Rate denominators</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>This system NEVER writes to Amazon. Section 2.7's automatic SP-API push is out of workbench scope. add_target is a recommendation; a person applies it.</t>
+          <t>Verified against Amazon's own stored columns: asin_share = ASIN impressions / total query impressions · click_rate = total clicks / SEARCH VOLUME (not impressions) · asin_click_share = ASIN clicks / total clicks. Recomputed from summed numerator and denominator, never averaged across weeks.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Deviation from source</t>
+          <t>SCOPE BOUNDARY</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Zero-sales is anchored on the product catalogue, not the sales report: that report only lists an ASIN on days it had traffic, so 27% of ASINs — the deadest ones — never appear in it.</t>
+          <t>This system NEVER writes to Amazon. Section 2.7's automatic SP-API push is out of workbench scope. add_target is a recommendation; a person applies it.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>QA (source 2.10)</t>
+          <t>Deviation from source</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>1_account_separation=PASS; 2_sku_mismatch_never_paired=PASS; 3_one_place_is_enough=PASS; 4_dual_method_independent=PASS; 5_directional_add_logic=PASS; 6_zero_manual_lookup=PASS; 7_monthly_cadence=PASS</t>
+          <t>Zero-sales is anchored on the product catalogue, not the sales report: that report only lists an ASIN on days it had traffic, so 27% of ASINs — the deadest ones — never appear in it.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>QA (source 2.10)</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>1_account_separation=PASS; 2_sku_mismatch_never_paired=PASS; 3_one_place_is_enough=PASS; 4_dual_method_independent=PASS; 5_directional_add_logic=PASS; 6_zero_manual_lookup=PASS; 7_monthly_cadence=PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>DRAFT — not validated, not published, not automated. Business confirmation from Thuwaraga still outstanding; rules confirmed by Abiraj 2026-08-19.</t>
         </is>

--- a/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D01_sqp_top_terms.xlsx
+++ b/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D01_sqp_top_terms.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19T15:18:23</t>
+          <t>2026-08-19T15:55:01</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>1_account_separation=PASS; 2_sku_mismatch_never_paired=PASS; 3_one_place_is_enough=PASS; 4_dual_method_independent=PASS; 5_directional_add_logic=PASS; 6_zero_manual_lookup=PASS; 7_monthly_cadence=PASS</t>
+          <t>1_account_separation=PASS; 2_sku_mismatch_never_paired=PASS; 3_one_place_is_enough=PASS; 4_dual_method_independent=PASS; 5_directional_add_logic=PASS; 6_zero_manual_lookup=PASS; 8_every_asin_accounted_for=PASS; 7_monthly_cadence=PASS</t>
         </is>
       </c>
     </row>

--- a/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D01_sqp_top_terms.xlsx
+++ b/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D01_sqp_top_terms.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19T15:55:01</t>
+          <t>2026-08-19T16:06:04</t>
         </is>
       </c>
     </row>

--- a/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D01_sqp_top_terms.xlsx
+++ b/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D01_sqp_top_terms.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19T16:06:04</t>
+          <t>2026-08-19T16:20:33</t>
         </is>
       </c>
     </row>

--- a/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D01_sqp_top_terms.xlsx
+++ b/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D01_sqp_top_terms.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19T16:20:33</t>
+          <t>2026-08-19T16:40:50</t>
         </is>
       </c>
     </row>

--- a/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D01_sqp_top_terms.xlsx
+++ b/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D01_sqp_top_terms.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19T16:40:50</t>
+          <t>2026-08-19T17:22:10</t>
         </is>
       </c>
     </row>

--- a/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D01_sqp_top_terms.xlsx
+++ b/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D01_sqp_top_terms.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19T17:22:10</t>
+          <t>2026-08-19T17:36:04</t>
         </is>
       </c>
     </row>
